--- a/범운해운항공_전체데이터_통합백업_2026-10-21.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-21.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE63"/>
+  <dimension ref="A1:AE64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8318,6 +8318,139 @@
       </c>
       <c r="AE63" t="n">
         <v>4.11</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>수출 (Export)</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>BW-2026-067</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>BW260016</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>중국</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>대한민국 (KOREA)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>텐트러스트</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>余涛</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>윤세형</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>해상(LCL)</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Door To Door</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>1 박스 (CTN)</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>45×32×19cm(1CTN)</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>0.028 CBM</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>5</v>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>📦 물류센터 입고 및 접수 완료</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>미수</t>
+        </is>
+      </c>
+      <c r="T64" t="n">
+        <v>150000</v>
+      </c>
+      <c r="U64" t="n">
+        <v>123000</v>
+      </c>
+      <c r="V64" t="n">
+        <v>27000</v>
+      </c>
+      <c r="W64" t="inlineStr"/>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>潍坊市奎文区恒大名都26号楼 余涛</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>17589745505</t>
+        </is>
+      </c>
+      <c r="AC64" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>4.86</v>
       </c>
     </row>
   </sheetData>
@@ -8972,7 +9105,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형", "케이글로발"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}, "케이글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18000, "추가단가": 18000, "1CBM당단가": 0}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}, "케이글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장", "지급상태": "지급완료"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710", "지급상태": "지급완료"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사", "지급상태": "미지급"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 38000, "1CBM당단가": 0}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형", "케이글로발"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}, "케이글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18000, "추가단가": 18000, "1CBM당단가": 0}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}, "케이글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장", "지급상태": "지급완료"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710", "지급상태": "지급완료"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사", "지급상태": "미지급"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>

--- a/범운해운항공_전체데이터_통합백업_2026-10-21.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-21.xlsx
@@ -4167,7 +4167,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>BW260010</t>
+          <t xml:space="preserve">DPK365117536147  </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -4266,8 +4266,16 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr"/>
-      <c r="AB31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr"/>
       <c r="AE31" t="inlineStr"/>

--- a/범운해운항공_전체데이터_통합백업_2026-10-21.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-21.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE64"/>
+  <dimension ref="A1:AE65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8424,10 +8424,10 @@
         <v>150000</v>
       </c>
       <c r="U64" t="n">
-        <v>123000</v>
+        <v>103600</v>
       </c>
       <c r="V64" t="n">
-        <v>27000</v>
+        <v>46400</v>
       </c>
       <c r="W64" t="inlineStr"/>
       <c r="X64" t="inlineStr">
@@ -8437,7 +8437,7 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr"/>
@@ -8459,6 +8459,139 @@
       </c>
       <c r="AE64" t="n">
         <v>4.86</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>수출 (Export)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>BW-2026-068</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>BW260017</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>중국</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>대한민국 (KOREA)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>주식회사 조은로직스</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>河美兰</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>윤세형</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>해상(LCL)</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Door To Door</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>1 박스 (CTN)</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>0.000 CBM</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>32</v>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>📦 물류센터 입고 및 접수 완료</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>미수</t>
+        </is>
+      </c>
+      <c r="T65" t="n">
+        <v>480000</v>
+      </c>
+      <c r="U65" t="n">
+        <v>384000</v>
+      </c>
+      <c r="V65" t="n">
+        <v>96000</v>
+      </c>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>东莞市寮步镇和合园汇富中心A座313室  收件人</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13480021737</t>
+        </is>
+      </c>
+      <c r="AC65" t="n">
+        <v>32</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/범운해운항공_전체데이터_통합백업_2026-10-21.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-21.xlsx
@@ -4266,16 +4266,8 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr"/>
       <c r="AE31" t="inlineStr"/>
@@ -7972,7 +7964,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>케이글로발</t>
+          <t>유에스퀵</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -8006,10 +7998,10 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q61" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R61" t="inlineStr">
         <is>
@@ -8022,13 +8014,13 @@
         </is>
       </c>
       <c r="T61" t="n">
-        <v>438000</v>
+        <v>411120</v>
       </c>
       <c r="U61" t="n">
-        <v>387000</v>
+        <v>338400</v>
       </c>
       <c r="V61" t="n">
-        <v>51000</v>
+        <v>72720</v>
       </c>
       <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr">
@@ -8053,13 +8045,13 @@
         </is>
       </c>
       <c r="AC61" t="n">
-        <v>16.8</v>
+        <v>17.3</v>
       </c>
       <c r="AD61" t="n">
-        <v>16.8</v>
+        <v>17.3</v>
       </c>
       <c r="AE61" t="n">
-        <v>16.8</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="62">
@@ -8105,7 +8097,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>케이글로발</t>
+          <t>유에스퀵</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -8142,7 +8134,7 @@
         <v>48</v>
       </c>
       <c r="Q62" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="R62" t="inlineStr">
         <is>
@@ -8155,15 +8147,19 @@
         </is>
       </c>
       <c r="T62" t="n">
-        <v>1096320</v>
+        <v>1672320</v>
       </c>
       <c r="U62" t="n">
-        <v>888000</v>
+        <v>1305000</v>
       </c>
       <c r="V62" t="n">
-        <v>208320</v>
-      </c>
-      <c r="W62" t="inlineStr"/>
+        <v>367320</v>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>ups 1day 서비스요청건 kg당12000원 청구 완료</t>
+        </is>
+      </c>
       <c r="X62" t="inlineStr">
         <is>
           <t>이상복</t>
